--- a/Assets/Resources/Story/default.xlsx
+++ b/Assets/Resources/Story/default.xlsx
@@ -954,34 +954,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="1"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1">
-        <v>1</v>
-      </c>
-      <c r="B1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>22</v>
-      </c>
-      <c r="B3">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
